--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. NAVIA LA MAGAYA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. NAVIA LA MAGAYA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. LUCENTE</t>
+          <t>S. SHARASHIDZE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>40.8263</v>
+        <v>14.5263</v>
       </c>
       <c r="E2" t="n">
-        <v>29.5514</v>
+        <v>11.9637</v>
       </c>
       <c r="F2" t="n">
-        <v>11.2746</v>
+        <v>2.5626</v>
       </c>
       <c r="G2" t="n">
-        <v>21.4617</v>
+        <v>15.6004</v>
       </c>
       <c r="H2" t="n">
-        <v>20.3894</v>
+        <v>10.9605</v>
       </c>
       <c r="I2" t="n">
-        <v>1.072999999999999</v>
+        <v>4.639899999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>45.247</v>
+        <v>37.7833</v>
       </c>
       <c r="K2" t="n">
-        <v>34.2321</v>
+        <v>23.7105</v>
       </c>
       <c r="L2" t="n">
-        <v>11.0151</v>
+        <v>14.0729</v>
       </c>
       <c r="M2" t="n">
-        <v>-23.785</v>
+        <v>-22.1829</v>
       </c>
       <c r="N2" t="n">
-        <v>-13.8429</v>
+        <v>-12.7502</v>
       </c>
       <c r="O2" t="n">
-        <v>-9.9419</v>
+        <v>-9.432399999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>-27.4186</v>
+        <v>-6.462899999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-63.2588</v>
+        <v>-47.1992</v>
       </c>
       <c r="R2" t="n">
-        <v>35.8399</v>
+        <v>40.7361</v>
       </c>
       <c r="S2" t="n">
-        <v>44.6147</v>
+        <v>-2.8291</v>
       </c>
       <c r="T2" t="n">
-        <v>28.193</v>
+        <v>-3.5801</v>
       </c>
       <c r="U2" t="n">
-        <v>16.4214</v>
+        <v>0.7513000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1685</v>
+        <v>8.2178</v>
       </c>
       <c r="W2" t="n">
-        <v>19.3706</v>
+        <v>24.9606</v>
       </c>
       <c r="X2" t="n">
-        <v>-17.2023</v>
+        <v>-16.7427</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. NJIE</t>
+          <t>I. LUCENTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>22.1868</v>
+        <v>10.1991</v>
       </c>
       <c r="E3" t="n">
-        <v>16.7755</v>
+        <v>6.2318</v>
       </c>
       <c r="F3" t="n">
-        <v>5.411099999999999</v>
+        <v>3.967300000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9303000000000003</v>
+        <v>21.4617</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1679</v>
+        <v>20.3894</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.2379</v>
+        <v>1.072999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>16.8056</v>
+        <v>45.247</v>
       </c>
       <c r="K3" t="n">
-        <v>9.076700000000001</v>
+        <v>34.2321</v>
       </c>
       <c r="L3" t="n">
-        <v>7.7289</v>
+        <v>11.0151</v>
       </c>
       <c r="M3" t="n">
-        <v>-15.8759</v>
+        <v>-23.785</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.9091</v>
+        <v>-13.8429</v>
       </c>
       <c r="O3" t="n">
-        <v>-9.9665</v>
+        <v>-9.9419</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.5459</v>
+        <v>-27.4186</v>
       </c>
       <c r="Q3" t="n">
-        <v>-32.5106</v>
+        <v>-63.2588</v>
       </c>
       <c r="R3" t="n">
-        <v>29.9645</v>
+        <v>35.8399</v>
       </c>
       <c r="S3" t="n">
-        <v>42.1721</v>
+        <v>13.9876</v>
       </c>
       <c r="T3" t="n">
-        <v>30.8541</v>
+        <v>4.8737</v>
       </c>
       <c r="U3" t="n">
-        <v>11.318</v>
+        <v>9.114000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-18.3691</v>
+        <v>2.1685</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6272</v>
+        <v>19.3706</v>
       </c>
       <c r="X3" t="n">
-        <v>-19.9963</v>
+        <v>-17.2023</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. SHARASHIDZE</t>
+          <t>J. PRIETO LORIENTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>3.373199999999998</v>
+        <v>4.147300000000002</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1802</v>
+        <v>-4.051000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.806799999999999</v>
+        <v>8.198300000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>15.6004</v>
+        <v>1.663599999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>10.9605</v>
+        <v>-4.603400000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>4.639899999999999</v>
+        <v>6.266899999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>37.7833</v>
+        <v>31.7969</v>
       </c>
       <c r="K4" t="n">
-        <v>23.7105</v>
+        <v>13.4122</v>
       </c>
       <c r="L4" t="n">
-        <v>14.0729</v>
+        <v>18.3849</v>
       </c>
       <c r="M4" t="n">
-        <v>-22.1829</v>
+        <v>-30.1331</v>
       </c>
       <c r="N4" t="n">
-        <v>-12.7502</v>
+        <v>-18.0156</v>
       </c>
       <c r="O4" t="n">
-        <v>-9.432399999999999</v>
+        <v>-12.1179</v>
       </c>
       <c r="P4" t="n">
-        <v>-6.462899999999999</v>
+        <v>-15.8637</v>
       </c>
       <c r="Q4" t="n">
-        <v>-47.1992</v>
+        <v>-70.11369999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>40.7361</v>
+        <v>54.2497</v>
       </c>
       <c r="S4" t="n">
-        <v>-13.9819</v>
+        <v>-4.4018</v>
       </c>
       <c r="T4" t="n">
-        <v>-10.3635</v>
+        <v>-7.7012</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.6184</v>
+        <v>3.2993</v>
       </c>
       <c r="V4" t="n">
-        <v>8.2178</v>
+        <v>22.7498</v>
       </c>
       <c r="W4" t="n">
-        <v>24.9606</v>
+        <v>41.9677</v>
       </c>
       <c r="X4" t="n">
-        <v>-16.7427</v>
+        <v>-19.2178</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.7679</v>
+        <v>-1.8924</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4485</v>
+        <v>-0.6532</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3194</v>
+        <v>-1.2392</v>
       </c>
       <c r="G5" t="n">
         <v>-1.3286</v>
@@ -844,13 +844,13 @@
         <v>0.3916</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1481</v>
+        <v>0.02379999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4446</v>
+        <v>0.24</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2965</v>
+        <v>-0.2162</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ONWUKA ONWUKA</t>
+          <t>P. NJIE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>-9.073400000000001</v>
+        <v>-3.069799999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-13.3397</v>
+        <v>-3.5003</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2662</v>
+        <v>0.4305000000000003</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2389</v>
+        <v>0.9303000000000003</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8967</v>
+        <v>3.1679</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.657699999999998</v>
+        <v>-2.2379</v>
       </c>
       <c r="J6" t="n">
-        <v>7.7218</v>
+        <v>16.8056</v>
       </c>
       <c r="K6" t="n">
-        <v>5.7634</v>
+        <v>9.076700000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>1.958600000000001</v>
+        <v>7.7289</v>
       </c>
       <c r="M6" t="n">
-        <v>-6.4829</v>
+        <v>-15.8759</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8666</v>
+        <v>-5.9091</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.6163</v>
+        <v>-9.9665</v>
       </c>
       <c r="P6" t="n">
-        <v>-16.843</v>
+        <v>-2.5459</v>
       </c>
       <c r="Q6" t="n">
-        <v>-28.9856</v>
+        <v>-32.5106</v>
       </c>
       <c r="R6" t="n">
-        <v>12.1426</v>
+        <v>29.9645</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6283</v>
+        <v>16.9154</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.6096</v>
+        <v>10.578</v>
       </c>
       <c r="U6" t="n">
-        <v>6.2379</v>
+        <v>6.3373</v>
       </c>
       <c r="V6" t="n">
-        <v>2.9023</v>
+        <v>-18.3691</v>
       </c>
       <c r="W6" t="n">
-        <v>10.5336</v>
+        <v>1.6272</v>
       </c>
       <c r="X6" t="n">
-        <v>-7.6315</v>
+        <v>-19.9963</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>-9.6805</v>
+        <v>-7.067399999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.8567</v>
+        <v>-4.671600000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.823999999999999</v>
+        <v>-2.3964</v>
       </c>
       <c r="G7" t="n">
         <v>-3.628499999999999</v>
@@ -1000,13 +1000,13 @@
         <v>6.8545</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7991</v>
+        <v>0.8135999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6808999999999999</v>
+        <v>0.5043</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1179</v>
+        <v>0.3101</v>
       </c>
       <c r="V7" t="n">
         <v>-6.7991</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PRIETO LORIENTE</t>
+          <t>D. ONWUKA ONWUKA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>-12.1475</v>
+        <v>-7.764099999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-16.9545</v>
+        <v>-9.6921</v>
       </c>
       <c r="F8" t="n">
-        <v>4.806699999999999</v>
+        <v>1.927899999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>1.663599999999999</v>
+        <v>1.2389</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.603400000000001</v>
+        <v>3.8967</v>
       </c>
       <c r="I8" t="n">
-        <v>6.266899999999999</v>
+        <v>-2.657699999999998</v>
       </c>
       <c r="J8" t="n">
-        <v>31.7969</v>
+        <v>7.7218</v>
       </c>
       <c r="K8" t="n">
-        <v>13.4122</v>
+        <v>5.7634</v>
       </c>
       <c r="L8" t="n">
-        <v>18.3849</v>
+        <v>1.958600000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-30.1331</v>
+        <v>-6.4829</v>
       </c>
       <c r="N8" t="n">
-        <v>-18.0156</v>
+        <v>-1.8666</v>
       </c>
       <c r="O8" t="n">
-        <v>-12.1179</v>
+        <v>-4.6163</v>
       </c>
       <c r="P8" t="n">
-        <v>-15.8637</v>
+        <v>-16.843</v>
       </c>
       <c r="Q8" t="n">
-        <v>-70.11369999999999</v>
+        <v>-28.9856</v>
       </c>
       <c r="R8" t="n">
-        <v>54.2497</v>
+        <v>12.1426</v>
       </c>
       <c r="S8" t="n">
-        <v>-20.6975</v>
+        <v>4.9376</v>
       </c>
       <c r="T8" t="n">
-        <v>-20.6049</v>
+        <v>1.0379</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.09229999999999974</v>
+        <v>3.8995</v>
       </c>
       <c r="V8" t="n">
-        <v>22.7498</v>
+        <v>2.9023</v>
       </c>
       <c r="W8" t="n">
-        <v>41.9677</v>
+        <v>10.5336</v>
       </c>
       <c r="X8" t="n">
-        <v>-19.2178</v>
+        <v>-7.6315</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>-18.8012</v>
+        <v>-15.0368</v>
       </c>
       <c r="E9" t="n">
-        <v>-11.8448</v>
+        <v>-10.8745</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.9565</v>
+        <v>-4.1625</v>
       </c>
       <c r="G9" t="n">
         <v>-13.3409</v>
@@ -1156,13 +1156,13 @@
         <v>16.4508</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.4759</v>
+        <v>1.2889</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4105</v>
+        <v>0.5599999999999998</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.0653</v>
+        <v>0.7290000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>-10.0352</v>
@@ -1189,13 +1189,13 @@
         <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>-26.5378</v>
+        <v>-17.2125</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.5592</v>
+        <v>-7.073399999999998</v>
       </c>
       <c r="F10" t="n">
-        <v>-15.9786</v>
+        <v>-10.1388</v>
       </c>
       <c r="G10" t="n">
         <v>-8.956000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>25.8516</v>
       </c>
       <c r="S10" t="n">
-        <v>-13.1705</v>
+        <v>-3.845</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.122300000000001</v>
+        <v>0.3633000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-10.0481</v>
+        <v>-4.2084</v>
       </c>
       <c r="V10" t="n">
         <v>-10.6782</v>
@@ -1267,13 +1267,13 @@
         <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>-27.9753</v>
+        <v>-22.05</v>
       </c>
       <c r="E11" t="n">
-        <v>-20.2788</v>
+        <v>-16.5387</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.696400000000001</v>
+        <v>-5.511200000000001</v>
       </c>
       <c r="G11" t="n">
         <v>5.463299999999999</v>
@@ -1312,13 +1312,13 @@
         <v>30.5519</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.031</v>
+        <v>4.8946</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.2275</v>
+        <v>-0.4878000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>3.1967</v>
+        <v>5.3822</v>
       </c>
       <c r="V11" t="n">
         <v>-14.5858</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ LUQUE</t>
+          <t>J. GONZALEZ DACAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>-44.0911</v>
+        <v>-36.1572</v>
       </c>
       <c r="E12" t="n">
-        <v>-42.6211</v>
+        <v>-39.6057</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4704</v>
+        <v>3.4481</v>
       </c>
       <c r="G12" t="n">
-        <v>-22.8431</v>
+        <v>-26.5767</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.6773</v>
+        <v>-17.5324</v>
       </c>
       <c r="I12" t="n">
-        <v>-19.1657</v>
+        <v>-9.0443</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.023299999999999</v>
+        <v>-3.8957</v>
       </c>
       <c r="K12" t="n">
-        <v>5.9773</v>
+        <v>-5.3238</v>
       </c>
       <c r="L12" t="n">
-        <v>-9.000299999999999</v>
+        <v>1.4278</v>
       </c>
       <c r="M12" t="n">
-        <v>-19.8197</v>
+        <v>-22.6811</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.6546</v>
+        <v>-12.2087</v>
       </c>
       <c r="O12" t="n">
-        <v>-10.1654</v>
+        <v>-10.4721</v>
       </c>
       <c r="P12" t="n">
-        <v>-11.9466</v>
+        <v>-9.400700000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-38.778</v>
+        <v>-47.9826</v>
       </c>
       <c r="R12" t="n">
-        <v>26.8311</v>
+        <v>38.5818</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.371099999999999</v>
+        <v>0.8396000000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>-8.5421</v>
+        <v>-1.532</v>
       </c>
       <c r="U12" t="n">
-        <v>3.1708</v>
+        <v>2.3719</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.9304</v>
+        <v>-1.0195</v>
       </c>
       <c r="W12" t="n">
-        <v>7.7226</v>
+        <v>13.8058</v>
       </c>
       <c r="X12" t="n">
-        <v>-11.653</v>
+        <v>-14.8253</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. GONZALEZ DACAL</t>
+          <t>G. RODRIGUEZ LUQUE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>-46.2824</v>
+        <v>-38.7395</v>
       </c>
       <c r="E13" t="n">
-        <v>-44.6292</v>
+        <v>-36.8343</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.652999999999999</v>
+        <v>-1.9054</v>
       </c>
       <c r="G13" t="n">
-        <v>-26.5767</v>
+        <v>-22.8431</v>
       </c>
       <c r="H13" t="n">
-        <v>-17.5324</v>
+        <v>-3.6773</v>
       </c>
       <c r="I13" t="n">
-        <v>-9.0443</v>
+        <v>-19.1657</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.8957</v>
+        <v>-3.023299999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.3238</v>
+        <v>5.9773</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4278</v>
+        <v>-9.000299999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-22.6811</v>
+        <v>-19.8197</v>
       </c>
       <c r="N13" t="n">
-        <v>-12.2087</v>
+        <v>-9.6546</v>
       </c>
       <c r="O13" t="n">
-        <v>-10.4721</v>
+        <v>-10.1654</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.400700000000001</v>
+        <v>-11.9466</v>
       </c>
       <c r="Q13" t="n">
-        <v>-47.9826</v>
+        <v>-38.778</v>
       </c>
       <c r="R13" t="n">
-        <v>38.5818</v>
+        <v>26.8311</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.285600000000001</v>
+        <v>-0.01940000000000014</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.5561</v>
+        <v>-2.7554</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.7293</v>
+        <v>2.736</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0195</v>
+        <v>-3.9304</v>
       </c>
       <c r="W13" t="n">
-        <v>13.8058</v>
+        <v>7.7226</v>
       </c>
       <c r="X13" t="n">
-        <v>-14.8253</v>
+        <v>-11.653</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>-58.3587</v>
+        <v>-48.4005</v>
       </c>
       <c r="E14" t="n">
-        <v>-42.8919</v>
+        <v>-36.2176</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.4666</v>
+        <v>-12.183</v>
       </c>
       <c r="G14" t="n">
         <v>-3.9321</v>
@@ -1546,13 +1546,13 @@
         <v>21.1514</v>
       </c>
       <c r="S14" t="n">
-        <v>-14.5983</v>
+        <v>-4.64</v>
       </c>
       <c r="T14" t="n">
-        <v>-9.7294</v>
+        <v>-3.0547</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.8688</v>
+        <v>-1.5851</v>
       </c>
       <c r="V14" t="n">
         <v>-10.4508</v>
@@ -1579,16 +1579,16 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-188.3295</v>
+        <v>-168.5175</v>
       </c>
       <c r="E15" t="n">
-        <v>-157.9173</v>
+        <v>-151.5169</v>
       </c>
       <c r="F15" t="n">
-        <v>-30.4131</v>
+        <v>-17.0018</v>
       </c>
       <c r="G15" t="n">
-        <v>-34.24770000000001</v>
+        <v>-34.2477</v>
       </c>
       <c r="H15" t="n">
         <v>3.778</v>
@@ -1603,7 +1603,7 @@
         <v>107.4989</v>
       </c>
       <c r="L15" t="n">
-        <v>61.5613</v>
+        <v>61.56130000000001</v>
       </c>
       <c r="M15" t="n">
         <v>-203.3081</v>
@@ -1624,13 +1624,13 @@
         <v>339.5975</v>
       </c>
       <c r="S15" t="n">
-        <v>8.152299999999999</v>
+        <v>27.9658</v>
       </c>
       <c r="T15" t="n">
-        <v>-7.355099999999999</v>
+        <v>-0.9540000000000002</v>
       </c>
       <c r="U15" t="n">
-        <v>15.5082</v>
+        <v>28.9209</v>
       </c>
       <c r="V15" t="n">
         <v>-39.8297</v>
